--- a/output_data/DC_PV_OG.xlsx
+++ b/output_data/DC_PV_OG.xlsx
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.04229621068741</v>
+        <v>139.7580089883161</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168.9768388783743</v>
+        <v>1024.892065914318</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>261.1460237211239</v>
+        <v>1583.924101867582</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>340.5139328912695</v>
+        <v>2065.312799494005</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>453.1651588101856</v>
+        <v>2748.574176770216</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>454.4452863774461</v>
+        <v>2756.3385106029</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>469.806817184571</v>
+        <v>2849.510516595111</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>464.6863069155294</v>
+        <v>2818.453181264374</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>474.9273274536127</v>
+        <v>2880.567851925848</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>380.1978874763422</v>
+        <v>2306.007148307215</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>298.2697231716759</v>
+        <v>1809.089783015425</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>216.3415588670096</v>
+        <v>1312.172417723634</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>139.5339048313849</v>
+        <v>846.3123877625807</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>40.96408215233317</v>
+        <v>248.4586826458953</v>
       </c>
     </row>
     <row r="21">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1280.127567260412</v>
+        <v>7764.333832684227</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/DC_PV_OG.xlsx
+++ b/output_data/DC_PV_OG.xlsx
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139.7580089883161</v>
+        <v>52.96776991656306</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1024.892065914318</v>
+        <v>388.4303127214625</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1583.924101867582</v>
+        <v>600.3013923877147</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2065.312799494005</v>
+        <v>782.7459332114321</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2748.574176770216</v>
+        <v>1041.69947502574</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2756.3385106029</v>
+        <v>1044.642128909994</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2849.510516595111</v>
+        <v>1079.953975521036</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2818.453181264374</v>
+        <v>1068.183359984022</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2880.567851925848</v>
+        <v>1091.72459105805</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2306.007148307215</v>
+        <v>873.9682036232906</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1809.089783015425</v>
+        <v>685.6383550310665</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1312.172417723634</v>
+        <v>497.3085064388422</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>846.3123877625807</v>
+        <v>320.7492733836319</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>248.4586826458953</v>
+        <v>94.16492429611212</v>
       </c>
     </row>
     <row r="21">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7764.333832684227</v>
+        <v>2942.653884253504</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/DC_PV_OG.xlsx
+++ b/output_data/DC_PV_OG.xlsx
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.96776991656306</v>
+        <v>52.47679948778589</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>388.4303127214625</v>
+        <v>384.8298629104299</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>600.3013923877147</v>
+        <v>594.7370608615734</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>782.7459332114321</v>
+        <v>775.4904813195027</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1041.69947502574</v>
+        <v>1032.043723259789</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1044.642128909994</v>
+        <v>1034.959101009111</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1079.953975521036</v>
+        <v>1069.943634000968</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1068.183359984022</v>
+        <v>1058.282123003682</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1091.72459105805</v>
+        <v>1081.605144998254</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>873.9682036232906</v>
+        <v>865.8671915484672</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>685.6383550310665</v>
+        <v>679.2830155918952</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>497.3085064388422</v>
+        <v>492.6988396353231</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>320.7492733836319</v>
+        <v>317.7761746760368</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>94.16492429611212</v>
+        <v>93.29208797828603</v>
       </c>
     </row>
     <row r="21">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2942.653884253504</v>
+        <v>2915.377749321438</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/DC_PV_OG.xlsx
+++ b/output_data/DC_PV_OG.xlsx
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.47679948778589</v>
+        <v>55.25380062479941</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>384.8298629104299</v>
+        <v>405.1945379151957</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>594.7370608615734</v>
+        <v>626.2097404143933</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>775.4904813195027</v>
+        <v>816.5283870109247</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1032.043723259789</v>
+        <v>1086.658078954388</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1034.959101009111</v>
+        <v>1089.727734544655</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1069.943634000968</v>
+        <v>1126.563601627855</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1058.282123003682</v>
+        <v>1114.284979266788</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1081.605144998254</v>
+        <v>1138.842223988921</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>865.8671915484672</v>
+        <v>911.6877103091903</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>679.2830155918952</v>
+        <v>715.2297525321258</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>492.6988396353231</v>
+        <v>518.7717947550613</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>317.7761746760368</v>
+        <v>334.5924593390631</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>93.29208797828603</v>
+        <v>98.2289788885323</v>
       </c>
     </row>
     <row r="21">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2915.377749321438</v>
+        <v>3069.655590266634</v>
       </c>
     </row>
   </sheetData>
